--- a/Lab06/Data/Measurements.xlsx
+++ b/Lab06/Data/Measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/g_tec/Git/EEK_lab/Lab06/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E337104-25D2-8A4A-B3FC-390CAD546823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE327446-798D-F644-932E-1F2DCBEBBFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20560" yWindow="800" windowWidth="20560" windowHeight="24140" xr2:uid="{2D9BB097-BA8F-D54D-A2F7-97E7F53D80D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
   <si>
     <t>settings generator</t>
   </si>
@@ -59,18 +59,12 @@
     <t>V</t>
   </si>
   <si>
-    <t>Vo fal time</t>
-  </si>
-  <si>
     <t>us</t>
   </si>
   <si>
     <t>Vo rise time</t>
   </si>
   <si>
-    <t>SR slew rate</t>
-  </si>
-  <si>
     <t>delta t avg</t>
   </si>
   <si>
@@ -204,6 +198,24 @@
   </si>
   <si>
     <t>R1 meas</t>
+  </si>
+  <si>
+    <t>SR avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR fall </t>
+  </si>
+  <si>
+    <t>Vo fall time</t>
+  </si>
+  <si>
+    <t>SR rise</t>
+  </si>
+  <si>
+    <t>SR avg time</t>
+  </si>
+  <si>
+    <t>1/4R1C (R2/R3)</t>
   </si>
 </sst>
 </file>
@@ -575,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BCCB8B-3EB5-A34A-93F0-61754F45EAFF}">
-  <dimension ref="A2:G68"/>
+  <dimension ref="A2:G71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
@@ -583,34 +595,34 @@
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>5.15</v>
@@ -622,359 +634,384 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>6.2080000000000002</v>
       </c>
       <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
       </c>
       <c r="B10">
         <v>8.3979999999999997</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f>(B9+B10)/2</f>
         <v>7.3029999999999999</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B12">
+        <f>B8/B9</f>
+        <v>0.82957474226804129</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <f>B8/B10</f>
+        <v>0.61324124791617063</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14">
+        <f>(B12+B13)/2</f>
+        <v>0.72140799509210596</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15">
         <f>B8/B11</f>
         <v>0.7051896480898262</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15">
-        <v>4.2949999999999999</v>
-      </c>
       <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>0.81399999999999995</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>4.3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>0.81399999999999995</v>
+        <v>4.2949999999999999</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B19">
-        <f>B16/B15</f>
-        <v>0.18952270081490105</v>
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B20">
+        <v>4.3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <f>B19/B18</f>
+        <v>0.18952270081490105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23">
         <f>(100*10^3)/100</f>
         <v>1000</v>
       </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
-        <f>20*LOG(B20/B19)</f>
-        <v>74.4467752655612</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>27</v>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24">
+        <f>20*LOG(B23/B22)</f>
+        <v>74.4467752655612</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <f>-(100*10^3)/(22*10^3)</f>
         <v>-4.5454545454545459</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
-      <c r="E24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25">
+      <c r="B28">
         <v>1.0074000000000001</v>
       </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26">
-        <v>4.508</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27">
-        <f>-B26/B25</f>
-        <v>-4.474885844748858</v>
-      </c>
-      <c r="D27" t="s">
-        <v>36</v>
+      <c r="C28" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>4.508</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30">
+        <f>-B29/B28</f>
+        <v>-4.474885844748858</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33">
         <f>-(100*10^3)/(100*10^3)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34">
         <v>1.0067999999999999</v>
       </c>
-      <c r="C31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>1.0074000000000001</v>
-      </c>
-      <c r="C32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <f>-B32/B31</f>
-        <v>-1.0005959475566151</v>
+      <c r="C34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="B35">
+        <v>1.0074000000000001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B36">
+        <f>-B35/B34</f>
+        <v>-1.0005959475566151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39">
         <f>1+(100*10^3)/(22*10^3)</f>
         <v>5.5454545454545459</v>
       </c>
-      <c r="D36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37">
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40">
         <v>1.0045999999999999</v>
       </c>
-      <c r="C37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38">
-        <v>5.4640000000000004</v>
-      </c>
-      <c r="C38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39">
-        <f>B38/B37</f>
-        <v>5.4389806888313768</v>
-      </c>
-      <c r="D39" t="s">
-        <v>34</v>
+      <c r="C40" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="B41">
+        <v>5.4640000000000004</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B42">
+        <f>B41/B40</f>
+        <v>5.4389806888313768</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45">
         <f>1+(100*10^3)/(100*10^3)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46">
         <v>1.0073000000000001</v>
       </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44">
-        <v>2.016</v>
-      </c>
-      <c r="C44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45">
-        <f>B44/B43</f>
-        <v>2.001389854065323</v>
+      <c r="C46" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="B47">
+        <v>2.016</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -982,215 +1019,230 @@
         <v>31</v>
       </c>
       <c r="B48">
-        <v>2.0118999999999998</v>
-      </c>
-      <c r="C48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>32</v>
-      </c>
-      <c r="B49">
-        <v>2.0116000000000001</v>
-      </c>
-      <c r="C49" t="s">
-        <v>6</v>
+        <f>B47/B46</f>
+        <v>2.001389854065323</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50">
-        <f>B49/B48</f>
-        <v>0.99985088722103499</v>
-      </c>
-      <c r="D50" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51">
+        <v>2.0118999999999998</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>30</v>
+      </c>
+      <c r="B52">
+        <v>2.0116000000000001</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B53">
+        <f>B52/B51</f>
+        <v>0.99985088722103499</v>
+      </c>
+      <c r="D53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56">
         <f>1*((100*10^3)/(100*10^3))+1*((100*10^3)/(22*10^3))</f>
         <v>5.5454545454545459</v>
       </c>
-      <c r="C53" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="C56" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" t="s">
         <v>44</v>
-      </c>
-      <c r="G53" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54">
-        <v>99.8</v>
-      </c>
-      <c r="C54" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55">
-        <v>100.03</v>
-      </c>
-      <c r="C55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56">
-        <v>22.117999999999999</v>
-      </c>
-      <c r="C56" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B57">
-        <f>1*(B54/B55)+1*(B55/B56)</f>
-        <v>5.5202614999928992</v>
+        <v>99.8</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B58">
-        <v>1.0061</v>
+        <v>100.03</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59">
-        <v>5.4260000000000002</v>
+        <v>22.117999999999999</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60">
+        <f>1*(B57/B58)+1*(B58/B59)</f>
+        <v>5.5202614999928992</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>49</v>
       </c>
-      <c r="B60">
-        <f>B58*(B54/B55)+B58*(B54/B56)</f>
-        <v>5.5434728924120487</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B61">
+        <v>1.0061</v>
+      </c>
+      <c r="C61" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="B62">
+        <v>5.4260000000000002</v>
+      </c>
+      <c r="C62" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B63">
+        <f>B61*(B57/B58)+B61*(B57/B59)</f>
+        <v>5.5434728924120487</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66">
         <f>1*((100*10^3)/(100*10^3))+1*((100*10^3)/(100*10^3))</f>
         <v>2</v>
       </c>
-      <c r="C63" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>53</v>
-      </c>
-      <c r="B64">
-        <v>99.87</v>
-      </c>
-      <c r="C64" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65">
-        <f>1*(B54/B55)+1*(B54/B64)</f>
-        <v>1.9969997786085221</v>
-      </c>
-      <c r="C65" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>51</v>
-      </c>
-      <c r="B66">
-        <v>1.0079</v>
-      </c>
       <c r="C66" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B67">
-        <v>2.0112999999999999</v>
+        <v>99.87</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68">
+        <f>1*(B57/B58)+1*(B57/B67)</f>
+        <v>1.9969997786085221</v>
+      </c>
+      <c r="C68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>49</v>
       </c>
-      <c r="B68">
-        <f>B66*(B54/B55)+B66*(B54/B64)</f>
+      <c r="B69">
+        <v>1.0079</v>
+      </c>
+      <c r="C69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>47</v>
+      </c>
+      <c r="B71">
+        <f>B69*(B57/B58)+B69*(B57/B67)</f>
         <v>2.0127760768595295</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C71" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>